--- a/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,147 +481,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M04_AU10</t>
+          <t>CF_M04_AU02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Component </t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
+          <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CF_M04_AU01</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Application Layer</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Relational database management system used for data persistence.</t>
+          <t>Includes the system's use cases, which orchestrate business logic and define the flow of operations.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7872</v>
+        <v>0.8548</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M04_AU12</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>CF_M04_AU10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t xml:space="preserve">Component </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>It acts as an intermediary between the domain and the infrastructure.</t>
+          <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>55</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M04_AU08, CF_M04_AU07, CF_M04_AU09</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>application layer, domain layer, infrastructure layer</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Domain Layer (Frontend)</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Contains business logic, use cases, entities, and repository interfaces.</t>
+          <t>Relational database management system used for data persistence.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7644</v>
+        <v>0.7872</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M04_AU20</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
+          <t>CF_M04_AU12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Users: Application customers who use the new features and provide feedback.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>It acts as an intermediary between the domain and the infrastructure.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>55</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M04_AU08, CF_M04_AU07, CF_M04_AU09</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>application layer, domain layer, infrastructure layer</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Domain Layer</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AI service provider used for Cintia functionality.</t>
+          <t>Contains the purest business logic of the system, as well as domain models and repository interfaces.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.718</v>
+        <v>0.7792</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M04_AU21</t>
+          <t>CF_M04_AU16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -632,146 +638,136 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>This confirmation allows the front-end to inform the user that they can enter the received code.</t>
+          <t>Integrations with external services such as Gemini, ChatGPT orFirebase.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M04_AU01, CF_M04_AU21</t>
+          <t>CF_M04_AU09, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>frontend</t>
+          <t>infrastructure layer, gemini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>The mobile application developed with Flutter that acts as the presentation layer, managing the graphical interface, navigation, and user interaction.</t>
+          <t>El sistema integra diversos serveis externs a través del back-end, com ara serveis d’intel·ligència artificial (Gemini o ChatGPT) i serveis d’autenticació.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7078</v>
+        <v>0.8525</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M04_AU24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
+          <t>CF_M04_AU19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
+          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M04_P08</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>CF_M04_AU04, CF_M04_AU18</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>backend, authentication service</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Presentation Layer (Frontend)</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Manages the application state and communication with the user interface using Bloc/Cubit.</t>
+          <t>Specialized service responsible for creating and sending OTP codes for delegated login.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.9486</v>
+        <v>0.7536</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M04_AU26</t>
+          <t>CF_M04_AU20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Google Login</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Authentication services, such as Google login.</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>73</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CF_M04_AU18</t>
-        </is>
-      </c>
+          <t>Users: Application customers who use the new features and provide feedback.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Google OAuth 2.0</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Authentication provider used for user login.</t>
+          <t>External AI service integrated into the system.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.795</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M04_AU28</t>
+          <t>CF_M04_AU21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -782,186 +778,482 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
+          <t>This confirmation allows the front-end to inform the user that they can enter the received code.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M04_AU23, CF_M04_AU04</t>
+          <t>CF_M04_AU01, CF_M04_AU21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>data, backend</t>
+          <t>frontend</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Data Layer (Frontend)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Handles data access, including backend calls, data transformation, and concrete repository implementations.</t>
+          <t>The mobile application developed with Flutter, which acts as the presentation layer.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7814</v>
+        <v>0.7078</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M04_P02</t>
+          <t>CF_M04_AU22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hierarchical model</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
+          <t>Domain: contains the business logic, with use cases, entities and repositories defined as interfaces.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M04_AU01</t>
+          <t>CF_M04_P08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Hexagonal Architecture</t>
+          <t>Domain Layer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>The back-end is implemented using Django and follows the Hexagonal Architecture (Ports and Adapters) pattern, which allows separating business logic from the framework and infrastructure technologies.</t>
+          <t>Contains the purest business logic of the system, as well as domain models and repository interfaces.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.6627</v>
+        <v>0.8591</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M04_P03</t>
+          <t>CF_M04_AU23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Modular architecture</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
+          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M04_AU01</t>
+          <t>CF_M04_P08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Hexagonal Architecture</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>The back-end is implemented using Django and follows the Hexagonal Architecture (Ports and Adapters) pattern, which allows separating business logic from the framework and infrastructure technologies.</t>
+          <t>Les dades s’intercanvien en format JSON, utilitzant mètodes HTTP estàndard com GET i POST.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.6897</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M04_P07</t>
+          <t>CF_M04_AU24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
+          <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M04_AU04</t>
+          <t>CF_M04_P08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Application Layer</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>The back-end uses MySQL for data persistence, managed through the Django ORM.</t>
+          <t>Includes the system's use cases, which orchestrate business logic and define the flow of operations.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.7118</v>
+        <v>0.8548</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M04_AU26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Google Login</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Authentication services, such as Google login.</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>73</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M04_AU18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Authentication Service</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Specialized service responsible for creating and sending OTP codes for delegated login.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6734</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M04_AU27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Firebase</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Firebase for complementary functionalities (notifications, services associated).</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>56</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>The server-side software responsible for processing user requests, implemented using Django.</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6827</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CF_M04_AU28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Data: handles data access, including calls to the backend, the data transformation and the specific implementation of the repositories.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>71</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CF_M04_AU23, CF_M04_AU04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>data, backend</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>The server-side software responsible for processing user requests, implemented using Django.</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.726</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CF_M04_P02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hierarchical model</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>57</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CF_M04_AU01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Domain Layer</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Contains the purest business logic of the system, as well as domain models and repository interfaces.</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6816</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CF_M04_P03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Modular architecture</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>62</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CF_M04_AU01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Hexagonal Architecture</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>The backend follows the Hexagonal Architecture (Ports and Adapters) pattern, which allows separating business logic from the framework and infrastructure technologies.</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.7586000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CF_M04_P07</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ORM</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>66</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CF_M04_AU04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>La persistència de les dades es realitza mitjançant una base de dades relacional MySQL, gestionada a través de l’ORM de Django.</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7435</v>
       </c>
     </row>
   </sheetData>
